--- a/output/pdf_financials_xlsx/OPHR.xlsx
+++ b/output/pdf_financials_xlsx/OPHR.xlsx
@@ -5679,16 +5679,16 @@
         <v>3.994307</v>
       </c>
       <c r="N92" s="3" t="n">
-        <v>0</v>
+        <v>4.390148</v>
       </c>
       <c r="O92" s="3" t="n">
-        <v>0</v>
+        <v>5.377412</v>
       </c>
       <c r="P92" s="3" t="n">
-        <v>0</v>
+        <v>7.20185</v>
       </c>
       <c r="Q92" s="3" t="n">
-        <v>0</v>
+        <v>7.20185</v>
       </c>
     </row>
     <row r="93">
@@ -7070,13 +7070,13 @@
         <v>-1.408052</v>
       </c>
       <c r="O118" s="3" t="n">
-        <v>0.39275</v>
+        <v>0.134108</v>
       </c>
       <c r="P118" s="3" t="n">
-        <v>3.500921</v>
+        <v>2.535598</v>
       </c>
       <c r="Q118" s="3" t="n">
-        <v>1.737013</v>
+        <v>-0.918906</v>
       </c>
     </row>
     <row r="119">
@@ -9320,7 +9320,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -10074,7 +10078,11 @@
           <t>Reserves 7</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E22" t="inlineStr">
         <is>
           <t>-</t>
@@ -11888,7 +11896,11 @@
           <t>Prepaids and deposits</t>
         </is>
       </c>
-      <c r="D41" t="inlineStr"/>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E41" t="inlineStr">
         <is>
           <t>-</t>
@@ -16808,7 +16820,11 @@
           <t>Exploration and evaluation expenditures 5</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -18996,7 +19012,11 @@
           <t>Exploration and evaluation expenditures 6</t>
         </is>
       </c>
-      <c r="D116" t="inlineStr"/>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NetOtherInvestingChanges</t>
+        </is>
+      </c>
       <c r="E116" t="inlineStr">
         <is>
           <t>-</t>
@@ -30247,7 +30267,7 @@
         <v>-0.00673</v>
       </c>
       <c r="F234" s="5" t="n">
-        <v>0.055487</v>
+        <v>-0.055487</v>
       </c>
       <c r="G234" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/OPHR.xlsx
+++ b/output/pdf_financials_xlsx/OPHR.xlsx
@@ -933,16 +933,16 @@
         <v>1.157225</v>
       </c>
       <c r="N10" s="3" t="n">
-        <v>0.141454</v>
+        <v>0.6102379999999999</v>
       </c>
       <c r="O10" s="3" t="n">
-        <v>0.1678</v>
+        <v>1.024415</v>
       </c>
       <c r="P10" s="3" t="n">
-        <v>0.253098</v>
+        <v>1.310323</v>
       </c>
       <c r="Q10" s="3" t="n">
-        <v>0.263631</v>
+        <v>0.671999</v>
       </c>
     </row>
     <row r="11">
@@ -992,16 +992,16 @@
         <v>-1.157225</v>
       </c>
       <c r="N11" s="3" t="n">
-        <v>-0.141454</v>
+        <v>-0.6102379999999999</v>
       </c>
       <c r="O11" s="3" t="n">
-        <v>-0.1678</v>
+        <v>-1.024415</v>
       </c>
       <c r="P11" s="3" t="n">
-        <v>-0.253098</v>
+        <v>-1.310323</v>
       </c>
       <c r="Q11" s="3" t="n">
-        <v>-0.263631</v>
+        <v>-0.671999</v>
       </c>
     </row>
     <row r="12">
@@ -1017,7 +1017,7 @@
         <v>0</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>3.2e-05</v>
       </c>
       <c r="E12" s="3" t="n">
         <v>0</v>
@@ -1940,7 +1940,7 @@
         <v>-0.055487</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-1.056511</v>
+        <v>-1.056543</v>
       </c>
       <c r="E27" s="3" t="n">
         <v>-0.967213</v>
@@ -2050,7 +2050,7 @@
         <v>-0.055487</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-1.056511</v>
+        <v>-1.056543</v>
       </c>
       <c r="E29" s="3" t="n">
         <v>-0.967213</v>
@@ -2335,43 +2335,43 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.097784</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.383419</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.281099</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.009741</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.035821</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.10446</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.039467</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.053058</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.060093</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.015079</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.209519</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>2.15356</v>
       </c>
       <c r="N34" s="3" t="n">
-        <v>0</v>
+        <v>0.568004</v>
       </c>
       <c r="O34" s="3" t="n">
         <v>1.85049</v>
@@ -2445,43 +2445,43 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.097784</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.383419</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.281099</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.009741</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.035821</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.10446</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.039467</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.053058</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.060093</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.035</v>
+        <v>0.050079</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.01</v>
+        <v>0.219519</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.06</v>
+        <v>2.21356</v>
       </c>
       <c r="N36" s="3" t="n">
-        <v>0.12</v>
+        <v>0.6880039999999999</v>
       </c>
       <c r="O36" s="3" t="n">
         <v>2.03049</v>
@@ -3105,43 +3105,43 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.097784</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.380387</v>
+        <v>0</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.281099</v>
+        <v>0</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.009741</v>
+        <v>0</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.06858</v>
+        <v>0.032759</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.161837</v>
+        <v>0.057377</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.042628</v>
+        <v>0.003161</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.128058</v>
+        <v>0.075</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.060093</v>
+        <v>0</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.023804</v>
+        <v>0.008725</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.199702</v>
+        <v>0</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>2.379074</v>
+        <v>0.225514</v>
       </c>
       <c r="N48" s="3" t="n">
-        <v>0.657327</v>
+        <v>0.089323</v>
       </c>
       <c r="O48" s="3" t="n">
         <v>0.176802</v>
@@ -9688,7 +9688,11 @@
           <t>Reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E18" t="inlineStr">
         <is>
           <t>-</t>
@@ -10178,7 +10182,7 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10364,7 +10368,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -10944,7 +10952,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -11626,7 +11638,7 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
@@ -14978,7 +14990,7 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E74" s="5" t="n">
@@ -16918,7 +16930,11 @@
           <t>Refund of reclamation deposits</t>
         </is>
       </c>
-      <c r="D94" t="inlineStr"/>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E94" t="inlineStr">
         <is>
           <t>-</t>
@@ -19110,7 +19126,11 @@
           <t>Refund of reclamation deposits 5</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
@@ -22004,7 +22024,11 @@
           <t>Effects of currency exchange rate changes on reclamation deposit 4</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr"/>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E147" t="inlineStr">
         <is>
           <t>-</t>
@@ -22592,7 +22616,11 @@
           <t>Reclamation deposits 4</t>
         </is>
       </c>
-      <c r="D153" t="inlineStr"/>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>ChangeInRestrictedCash</t>
+        </is>
+      </c>
       <c r="E153" t="inlineStr">
         <is>
           <t>-</t>
@@ -32000,7 +32028,7 @@
       </c>
       <c r="D252" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E252" t="inlineStr">
@@ -32069,13 +32097,13 @@
         </is>
       </c>
       <c r="R252" s="5" t="n">
-        <v>-1.024415</v>
+        <v>1.024415</v>
       </c>
       <c r="S252" s="5" t="n">
-        <v>-1.310323</v>
+        <v>1.310323</v>
       </c>
       <c r="T252" s="5" t="n">
-        <v>-0.671999</v>
+        <v>0.671999</v>
       </c>
     </row>
     <row r="253">
@@ -37852,7 +37880,7 @@
       </c>
       <c r="D313" t="inlineStr">
         <is>
-          <t>TotalExpenses</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E313" t="inlineStr">
@@ -37916,10 +37944,10 @@
         </is>
       </c>
       <c r="Q313" s="5" t="n">
-        <v>-0.6102379999999999</v>
+        <v>0.6102379999999999</v>
       </c>
       <c r="R313" s="5" t="n">
-        <v>-1.024415</v>
+        <v>1.024415</v>
       </c>
       <c r="S313" t="inlineStr">
         <is>
@@ -45704,7 +45732,7 @@
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">

--- a/output/pdf_financials_xlsx/OPHR.xlsx
+++ b/output/pdf_financials_xlsx/OPHR.xlsx
@@ -29614,7 +29614,11 @@
           <t>Share issued for cash</t>
         </is>
       </c>
-      <c r="D227" t="inlineStr"/>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E227" t="inlineStr">
         <is>
           <t>-</t>
@@ -30680,7 +30684,11 @@
           <t>Shares issued for cash</t>
         </is>
       </c>
-      <c r="D238" t="inlineStr"/>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E238" s="5" t="n">
         <v>0.1</v>
       </c>
